--- a/Platform/Platform.WebSite/ModuleResources/Other/SPA_ScoringInfo/ImportTemplates/施工正確性頁籤明細匯入範本.xlsx
+++ b/Platform/Platform.WebSite/ModuleResources/Other/SPA_ScoringInfo/ImportTemplates/施工正確性頁籤明細匯入範本.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFE43ECC-48FA-45DB-AAD8-E36322CD816D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212486\Desktop\供應商評鑑系統\SPA系統優化2.0\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BE79C7-0A8A-4D37-B2A1-EC6B5CFF5584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="23453" windowHeight="14648" xr2:uid="{2984F46C-2D94-4B4A-AD03-55CBAB69B2C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2984F46C-2D94-4B4A-AD03-55CBAB69B2C2}"/>
   </bookViews>
   <sheets>
     <sheet name="施工正確性" sheetId="3" r:id="rId1"/>
@@ -15,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -36,33 +30,96 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={A0606E3B-2BA1-47BB-A90B-E08B1AA811F6}</author>
-    <author>tc={E19EB027-2FA7-4E48-898A-E9EB5B1F559A}</author>
-    <author>tc={7CD96E4C-9F3C-4094-B4C7-42352BCB358F}</author>
+    <author>tc={9C822599-B341-4277-A607-0E8B763C68CF}</author>
+    <author>tc={D5312E79-A364-4C97-B0CE-00DEF845C123}</author>
+    <author>tc={917B7120-633A-448F-B050-FA3FB5CB99E0}</author>
+    <author>tc={AE1B2C77-80A8-4DE6-BF46-D87A3072D4E7}</author>
+    <author>tc={A0B0D47A-6C80-421D-9D74-50C6894F5F37}</author>
+    <author>tc={A7B950EF-BDFD-4617-91C3-040288E58B14}</author>
+    <author>tc={7B7F20C1-0181-4B01-849E-CC7C623913FC}</author>
+    <author>tc={6426EFF6-DAD0-4382-9EEB-6923FB0432C7}</author>
+    <author>tc={6AB401A8-BF01-4D36-88F5-8892B3C9FBB2}</author>
+    <author>tc={7707B65B-CB6C-4C7B-BF9D-277D6B3005A7}</author>
   </authors>
   <commentList>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{A0606E3B-2BA1-47BB-A90B-E08B1AA811F6}">
-      <text>
-        <t>[對話串註解]
-您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
-註解:
-    請輸入"Yes" 或"No"</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{E19EB027-2FA7-4E48-898A-E9EB5B1F559A}">
-      <text>
-        <t>[對話串註解]
-您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
-註解:
-    請輸入"Yes" 或"No"</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="2" shapeId="0" xr:uid="{7CD96E4C-9F3C-4094-B4C7-42352BCB358F}">
-      <text>
-        <t>[對話串註解]
-您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
-註解:
-    請輸入"Yes" 或"No"</t>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{9C822599-B341-4277-A607-0E8B763C68CF}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的評鑑期間一致</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="1" shapeId="0" xr:uid="{D5312E79-A364-4C97-B0CE-00DEF845C123}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的評鑑單位一致</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="2" shapeId="0" xr:uid="{917B7120-633A-448F-B050-FA3FB5CB99E0}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的服務對象一致</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="3" shapeId="0" xr:uid="{AE1B2C77-80A8-4DE6-BF46-D87A3072D4E7}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的評鑑項目一致</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="4" shapeId="0" xr:uid="{A0B0D47A-6C80-421D-9D74-50C6894F5F37}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的受評供應商一致</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="5" shapeId="0" xr:uid="{A7B950EF-BDFD-4617-91C3-040288E58B14}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    MO事件發生日期，格式:"YYYY/MM/DD"</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="6" shapeId="0" xr:uid="{7B7F20C1-0181-4B01-849E-CC7C623913FC}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    MO事件發生地點</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="7" shapeId="0" xr:uid="{6426EFF6-DAD0-4382-9EEB-6923FB0432C7}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    MO事件造成TEL財物損失，請填"Yes" ，沒有填"No"</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="8" shapeId="0" xr:uid="{6AB401A8-BF01-4D36-88F5-8892B3C9FBB2}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    MO事件造成客戶財物損失，請填"Yes" ，沒有填"No"</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="9" shapeId="0" xr:uid="{7707B65B-CB6C-4C7B-BF9D-277D6B3005A7}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    MO事件造成人身事故，請填"Yes" ，沒有填"No"</t>
       </text>
     </comment>
   </commentList>
@@ -120,7 +177,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -143,6 +200,12 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -226,7 +289,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="a92573" id="{B12AB65D-B880-4C4F-A754-7968F66048AE}" userId="S::a92573@e365.shop::a5c1d779-7da7-4f72-9b02-b37c31ccf028" providerId="AD"/>
+  <person displayName="TET SCM Chen, Grace" id="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" userId="S::grace2.chen@tel.com::6dbe00fd-a5fc-44db-ab99-cd07605e303e" providerId="AD"/>
 </personList>
 </file>
 
@@ -547,14 +610,35 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H1" dT="2026-07-17T23:58:11.10" personId="{B12AB65D-B880-4C4F-A754-7968F66048AE}" id="{A0606E3B-2BA1-47BB-A90B-E08B1AA811F6}">
-    <text>請輸入"Yes" 或"No"</text>
-  </threadedComment>
-  <threadedComment ref="I1" dT="2026-07-17T23:58:20.55" personId="{B12AB65D-B880-4C4F-A754-7968F66048AE}" id="{E19EB027-2FA7-4E48-898A-E9EB5B1F559A}">
-    <text>請輸入"Yes" 或"No"</text>
-  </threadedComment>
-  <threadedComment ref="J1" dT="2026-07-17T23:58:25.49" personId="{B12AB65D-B880-4C4F-A754-7968F66048AE}" id="{7CD96E4C-9F3C-4094-B4C7-42352BCB358F}">
-    <text>請輸入"Yes" 或"No"</text>
+  <threadedComment ref="A1" dT="2026-09-17T02:57:37.00" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{9C822599-B341-4277-A607-0E8B763C68CF}">
+    <text>須與系統上的評鑑期間一致</text>
+  </threadedComment>
+  <threadedComment ref="B1" dT="2026-09-17T02:57:51.28" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{D5312E79-A364-4C97-B0CE-00DEF845C123}">
+    <text>須與系統上的評鑑單位一致</text>
+  </threadedComment>
+  <threadedComment ref="C1" dT="2026-09-17T02:58:14.38" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{917B7120-633A-448F-B050-FA3FB5CB99E0}">
+    <text>須與系統上的服務對象一致</text>
+  </threadedComment>
+  <threadedComment ref="D1" dT="2026-09-17T02:58:34.54" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{AE1B2C77-80A8-4DE6-BF46-D87A3072D4E7}">
+    <text>須與系統上的評鑑項目一致</text>
+  </threadedComment>
+  <threadedComment ref="E1" dT="2026-09-17T02:58:57.50" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{A0B0D47A-6C80-421D-9D74-50C6894F5F37}">
+    <text>須與系統上的受評供應商一致</text>
+  </threadedComment>
+  <threadedComment ref="F1" dT="2026-09-23T09:51:00.63" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{A7B950EF-BDFD-4617-91C3-040288E58B14}">
+    <text>MO事件發生日期，格式:"YYYY/MM/DD"</text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2026-09-23T09:51:33.52" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{7B7F20C1-0181-4B01-849E-CC7C623913FC}">
+    <text>MO事件發生地點</text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2026-09-23T09:53:31.62" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{6426EFF6-DAD0-4382-9EEB-6923FB0432C7}">
+    <text>MO事件造成TEL財物損失，請填"Yes" ，沒有填"No"</text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2026-09-23T09:54:07.32" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{6AB401A8-BF01-4D36-88F5-8892B3C9FBB2}">
+    <text>MO事件造成客戶財物損失，請填"Yes" ，沒有填"No"</text>
+  </threadedComment>
+  <threadedComment ref="J1" dT="2026-09-23T09:54:32.91" personId="{728CD83A-C0E8-448F-B5C8-C1403366EF9B}" id="{7707B65B-CB6C-4C7B-BF9D-277D6B3005A7}">
+    <text>MO事件造成人身事故，請填"Yes" ，沒有填"No"</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -564,13 +648,13 @@
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="8" width="15.796875" customWidth="1"/>
+    <col min="1" max="8" width="15.81640625" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15.796875" customWidth="1"/>
-    <col min="11" max="11" width="25.796875" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" customWidth="1"/>
+    <col min="11" max="11" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.8" customHeight="1">
+    <row r="1" spans="1:11" ht="28.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
